--- a/data/trans_camb/IP15-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 5,97</t>
+          <t>-11,41; 5,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 1,6</t>
+          <t>-15,34; 1,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 12,64</t>
+          <t>-10,53; 11,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 10,03</t>
+          <t>-6,99; 10,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 2,92</t>
+          <t>-13,09; 3,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 23,52</t>
+          <t>0,68; 23,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 6,55</t>
+          <t>-6,1; 6,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 0,32</t>
+          <t>-12,13; -0,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 14,83</t>
+          <t>-0,52; 14,54</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 27,34</t>
+          <t>-34,75; 26,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 7,68</t>
+          <t>-47,08; 7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 56,63</t>
+          <t>-32,78; 46,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 47,69</t>
+          <t>-23,77; 51,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 15,68</t>
+          <t>-45,92; 18,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 115,73</t>
+          <t>1,44; 118,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; 30,56</t>
+          <t>-20,73; 27,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 1,5</t>
+          <t>-41,1; -1,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 65,24</t>
+          <t>-1,82; 63,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 12,57</t>
+          <t>0,2; 11,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 8,98</t>
+          <t>-2,98; 8,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 19,43</t>
+          <t>5,16; 19,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,88</t>
+          <t>-0,89; 11,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 2,41</t>
+          <t>-9,6; 1,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 14,37</t>
+          <t>-0,08; 13,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 9,94</t>
+          <t>1,34; 9,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,88</t>
+          <t>-4,14; 3,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 14,68</t>
+          <t>4,27; 14,87</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 90,88</t>
+          <t>0,7; 77,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 61,12</t>
+          <t>-15,78; 58,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,99; 131,18</t>
+          <t>27,88; 133,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 67,23</t>
+          <t>-3,33; 64,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 13,54</t>
+          <t>-42,08; 12,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 81,29</t>
+          <t>-1,61; 78,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 58,76</t>
+          <t>6,46; 58,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 22,67</t>
+          <t>-20,16; 21,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>22,04; 88,26</t>
+          <t>21,06; 89,63</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 8,66</t>
+          <t>-6,9; 8,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 8,31</t>
+          <t>-5,48; 9,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 11,58</t>
+          <t>-4,03; 11,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 9,09</t>
+          <t>-5,77; 8,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 8,15</t>
+          <t>-6,75; 7,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 12,33</t>
+          <t>-2,64; 11,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 5,81</t>
+          <t>-4,17; 6,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 6,28</t>
+          <t>-3,83; 6,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 9,51</t>
+          <t>-0,61; 10,11</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 64,26</t>
+          <t>-31,87; 58,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 59,15</t>
+          <t>-24,61; 69,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 84,08</t>
+          <t>-19,91; 84,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 73,18</t>
+          <t>-29,78; 60,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 63,15</t>
+          <t>-32,76; 51,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 94,26</t>
+          <t>-12,02; 91,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,5; 38,61</t>
+          <t>-20,54; 41,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 42,54</t>
+          <t>-19,43; 42,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 66,19</t>
+          <t>-3,15; 67,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 6,68</t>
+          <t>-6,1; 6,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 3,07</t>
+          <t>-9,31; 2,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 37,14</t>
+          <t>2,48; 34,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 0,69</t>
+          <t>-11,31; 1,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,22; -0,03</t>
+          <t>-12,45; 0,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 8,9</t>
+          <t>-4,53; 8,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,52</t>
+          <t>-6,7; 1,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -0,28</t>
+          <t>-9,15; -0,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 19,99</t>
+          <t>1,58; 18,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 51,71</t>
+          <t>-33,64; 50,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 25,93</t>
+          <t>-49,94; 23,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,06; 275,61</t>
+          <t>10,55; 253,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 5,67</t>
+          <t>-50,36; 10,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 0,73</t>
+          <t>-55,27; 4,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 52,86</t>
+          <t>-20,27; 53,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,54; 9,75</t>
+          <t>-34,91; 12,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,8; -1,56</t>
+          <t>-46,29; -0,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,27; 125,02</t>
+          <t>7,61; 120,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 6,0</t>
+          <t>-1,19; 5,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,73</t>
+          <t>-3,52; 2,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,55; 18,68</t>
+          <t>3,37; 19,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,37</t>
+          <t>-2,47; 4,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,64; -0,23</t>
+          <t>-6,91; -0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 7,6</t>
+          <t>0,53; 7,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,24</t>
+          <t>-0,96; 4,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,37</t>
+          <t>-4,44; 0,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,67</t>
+          <t>3,11; 11,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 35,93</t>
+          <t>-6,23; 33,43</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 16,14</t>
+          <t>-18,08; 16,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17,95; 107,36</t>
+          <t>17,42; 112,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 23,94</t>
+          <t>-11,14; 24,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,26; -1,01</t>
+          <t>-31,19; -0,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 41,43</t>
+          <t>2,39; 41,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 23,55</t>
+          <t>-4,67; 22,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 2,04</t>
+          <t>-21,34; 1,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,68; 61,83</t>
+          <t>15,21; 62,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 5,92</t>
+          <t>-11,6; 7,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 1,57</t>
+          <t>-15,17; 2,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 11,17</t>
+          <t>-11,02; 11,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 10,28</t>
+          <t>-7,16; 10,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 3,2</t>
+          <t>-13,56; 4,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 23,78</t>
+          <t>1,28; 24,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 6,26</t>
+          <t>-6,77; 5,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,13; -0,33</t>
+          <t>-11,74; 0,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 14,54</t>
+          <t>-1,86; 14,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 26,89</t>
+          <t>-35,55; 32,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 7,58</t>
+          <t>-47,92; 9,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 46,24</t>
+          <t>-34,75; 51,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 51,13</t>
+          <t>-24,12; 50,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,92; 18,09</t>
+          <t>-45,28; 22,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 118,34</t>
+          <t>3,31; 121,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 27,08</t>
+          <t>-23,19; 27,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,1; -1,17</t>
+          <t>-40,02; 0,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 63,31</t>
+          <t>-6,59; 65,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 11,32</t>
+          <t>0,17; 12,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 8,7</t>
+          <t>-2,77; 8,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,16; 19,61</t>
+          <t>5,58; 20,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 11,07</t>
+          <t>-1,3; 10,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 1,98</t>
+          <t>-9,02; 1,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 13,92</t>
+          <t>0,04; 14,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 9,77</t>
+          <t>1,21; 9,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,53</t>
+          <t>-4,86; 3,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 14,87</t>
+          <t>4,95; 14,79</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 77,21</t>
+          <t>0,77; 83,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 58,5</t>
+          <t>-14,57; 62,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,88; 133,66</t>
+          <t>27,2; 139,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 64,95</t>
+          <t>-5,96; 62,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 12,73</t>
+          <t>-40,14; 10,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 78,68</t>
+          <t>-0,42; 82,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 58,84</t>
+          <t>5,68; 57,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 21,73</t>
+          <t>-23,9; 20,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,06; 89,63</t>
+          <t>23,83; 86,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 8,34</t>
+          <t>-5,96; 9,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 9,18</t>
+          <t>-5,81; 8,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 11,41</t>
+          <t>-3,51; 11,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 8,13</t>
+          <t>-7,23; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 7,16</t>
+          <t>-6,36; 7,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 11,95</t>
+          <t>-2,09; 12,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,09</t>
+          <t>-4,16; 6,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 6,33</t>
+          <t>-3,45; 6,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 10,11</t>
+          <t>-0,63; 9,91</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,87; 58,14</t>
+          <t>-28,55; 64,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 69,07</t>
+          <t>-27,62; 66,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 84,27</t>
+          <t>-15,51; 82,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 60,45</t>
+          <t>-35,05; 59,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,76; 51,54</t>
+          <t>-30,2; 55,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 91,0</t>
+          <t>-10,68; 95,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 41,24</t>
+          <t>-22,08; 43,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 42,74</t>
+          <t>-17,74; 48,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 67,79</t>
+          <t>-3,25; 67,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 6,53</t>
+          <t>-5,45; 6,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 2,98</t>
+          <t>-8,51; 2,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 34,38</t>
+          <t>2,06; 34,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 1,44</t>
+          <t>-11,11; 0,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 0,66</t>
+          <t>-12,23; -0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 8,52</t>
+          <t>-5,21; 8,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 1,79</t>
+          <t>-7,11; 1,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,15; -0,34</t>
+          <t>-9,16; -0,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 18,42</t>
+          <t>1,27; 19,72</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 50,75</t>
+          <t>-30,86; 50,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,94; 23,66</t>
+          <t>-46,95; 22,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,55; 253,06</t>
+          <t>9,26; 261,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 10,5</t>
+          <t>-50,35; 3,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,27; 4,73</t>
+          <t>-54,93; -0,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,27; 53,51</t>
+          <t>-22,47; 51,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,91; 12,66</t>
+          <t>-36,28; 11,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,29; -0,64</t>
+          <t>-46,56; -2,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,61; 120,73</t>
+          <t>5,63; 116,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 5,73</t>
+          <t>-1,29; 5,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,82</t>
+          <t>-3,86; 2,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,37; 19,5</t>
+          <t>3,24; 18,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,39</t>
+          <t>-2,18; 4,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -0,09</t>
+          <t>-6,66; -0,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,5</t>
+          <t>0,37; 8,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,02</t>
+          <t>-0,58; 4,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,25</t>
+          <t>-4,04; 0,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 11,58</t>
+          <t>3,17; 10,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 33,43</t>
+          <t>-6,72; 34,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 16,95</t>
+          <t>-19,63; 15,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17,42; 112,51</t>
+          <t>16,31; 104,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 24,47</t>
+          <t>-10,22; 25,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,19; -0,16</t>
+          <t>-30,25; -0,48</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,39; 41,04</t>
+          <t>1,65; 44,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 22,57</t>
+          <t>-2,82; 23,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 1,47</t>
+          <t>-19,67; 2,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,21; 62,4</t>
+          <t>15,42; 56,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP15-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP15-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,06</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,81</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,12</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,44</t>
+          <t>5,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 7,06</t>
+          <t>-6,96; 10,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 2,2</t>
+          <t>-13,63; 2,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 11,77</t>
+          <t>-0,2; 21,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 10,43</t>
+          <t>-11,74; 5,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 4,17</t>
+          <t>-15,43; 1,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 24,21</t>
+          <t>-10,54; 12,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 5,84</t>
+          <t>-6,1; 6,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 0,04</t>
+          <t>-11,58; 0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 14,45</t>
+          <t>-2,08; 13,15</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-20,96%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-9,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-24,92%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-20,96%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>-0,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 32,62</t>
+          <t>-23,27; 47,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 9,99</t>
+          <t>-47,37; 15,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 51,8</t>
+          <t>-1,04; 103,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 50,7</t>
+          <t>-35,34; 27,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,28; 22,76</t>
+          <t>-47,82; 7,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 121,49</t>
+          <t>-34,54; 55,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 27,18</t>
+          <t>-21,83; 30,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 0,1</t>
+          <t>-40,51; 1,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 65,91</t>
+          <t>-7,98; 57,69</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,38</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,99</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,38</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>11,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,45</t>
+          <t>8,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 12,04</t>
+          <t>-0,98; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 8,96</t>
+          <t>-8,43; 2,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 20,32</t>
+          <t>-0,47; 13,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 10,86</t>
+          <t>0,82; 12,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 1,82</t>
+          <t>-2,44; 8,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 14,4</t>
+          <t>4,36; 18,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 9,56</t>
+          <t>1,28; 9,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,43</t>
+          <t>-4,32; 3,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 14,79</t>
+          <t>3,92; 13,57</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-16,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>34,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,55%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-16,84%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 83,21</t>
+          <t>-4,14; 67,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 62,08</t>
+          <t>-38,03; 13,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,2; 139,01</t>
+          <t>-1,08; 79,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 62,74</t>
+          <t>4,19; 90,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,14; 10,32</t>
+          <t>-14,05; 61,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 82,25</t>
+          <t>21,62; 120,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 57,92</t>
+          <t>5,97; 58,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 20,71</t>
+          <t>-21,08; 22,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,83; 86,56</t>
+          <t>18,87; 81,45</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,87</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>4,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 9,07</t>
+          <t>-6,47; 9,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 8,72</t>
+          <t>-6,33; 8,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 11,3</t>
+          <t>-2,04; 12,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 7,59</t>
+          <t>-6,75; 8,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 7,45</t>
+          <t>-5,91; 8,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 12,48</t>
+          <t>-3,64; 11,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 6,22</t>
+          <t>-4,07; 5,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 6,53</t>
+          <t>-3,65; 6,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 9,91</t>
+          <t>-0,72; 9,63</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>7,79%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 64,67</t>
+          <t>-30,83; 73,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 66,99</t>
+          <t>-30,61; 63,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 82,21</t>
+          <t>-10,25; 95,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 59,6</t>
+          <t>-31,59; 64,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 55,18</t>
+          <t>-28,19; 59,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 95,13</t>
+          <t>-17,85; 83,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 43,0</t>
+          <t>-20,5; 38,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 48,64</t>
+          <t>-19,16; 42,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 67,37</t>
+          <t>-3,96; 66,8</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-5,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-6,06</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-3,0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12,56</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-5,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,06</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>2,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 6,37</t>
+          <t>-11,6; 0,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 2,86</t>
+          <t>-12,22; -0,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 34,15</t>
+          <t>-4,7; 9,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 0,53</t>
+          <t>-5,76; 6,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,23; -0,34</t>
+          <t>-8,79; 3,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 8,47</t>
+          <t>-2,05; 10,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 1,66</t>
+          <t>-6,96; 1,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -0,47</t>
+          <t>-8,71; -0,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 19,72</t>
+          <t>-1,33; 7,81</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-27,51%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-31,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-19,09%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>79,85%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-27,51%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-31,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 50,08</t>
+          <t>-51,11; 5,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 22,42</t>
+          <t>-55,76; 0,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,26; 261,83</t>
+          <t>-21,07; 56,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 3,84</t>
+          <t>-31,89; 51,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,93; -0,92</t>
+          <t>-48,78; 25,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 51,18</t>
+          <t>-12,03; 81,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 11,37</t>
+          <t>-36,54; 9,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,56; -2,71</t>
+          <t>-44,8; -1,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 116,83</t>
+          <t>-7,02; 49,74</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,64</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,36</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8,45</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>4,37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>4,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,9</t>
+          <t>-2,38; 4,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,64</t>
+          <t>-6,64; -0,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,79</t>
+          <t>-0,82; 7,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,61</t>
+          <t>-0,75; 6,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; -0,1</t>
+          <t>-3,84; 2,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,13</t>
+          <t>0,88; 8,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,15</t>
+          <t>-0,93; 4,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,4</t>
+          <t>-4,4; 0,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,59</t>
+          <t>1,44; 6,84</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-16,89%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-1,65%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>45,94%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-16,89%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 34,41</t>
+          <t>-10,96; 23,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 15,96</t>
+          <t>-30,26; -1,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16,31; 104,05</t>
+          <t>-3,76; 38,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 25,21</t>
+          <t>-3,71; 35,93</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -0,48</t>
+          <t>-19,16; 16,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,65; 44,81</t>
+          <t>4,36; 49,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 23,35</t>
+          <t>-4,57; 23,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 2,2</t>
+          <t>-21,61; 2,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,42; 56,87</t>
+          <t>7,06; 38,42</t>
         </is>
       </c>
     </row>
